--- a/overtime/sample/2월 초과근무수당 산정서(1505함).xlsx
+++ b/overtime/sample/2월 초과근무수당 산정서(1505함).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AM27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,430 +540,577 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>김근홍</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>급여 세부내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>근무시간(시간)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>총 근무시간</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>총 복무규정시간</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="E13" t="inlineStr">
         <is>
-          <t>복무규정시간(시간)</t>
-        </is>
-      </c>
-      <c r="AL13" t="n">
+          <t>근무시간(시간)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI13" t="n">
         <v>190</v>
       </c>
-      <c r="AM13" t="n">
-        <v>120</v>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>총 근무시간</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>총 복무규정시간</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="E14" t="inlineStr">
         <is>
-          <t>시간외(시간)</t>
-        </is>
-      </c>
-      <c r="AI14" t="n">
-        <v>96</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>시간외(시간)</t>
-        </is>
+          <t>복무규정시간(시간)</t>
+        </is>
+      </c>
+      <c r="AL14" t="n">
+        <v>190</v>
       </c>
       <c r="AM14" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="E15" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
-        </is>
+          <t>시간외(시간)</t>
+        </is>
+      </c>
+      <c r="AI15" t="n">
+        <v>96</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
+          <t>시간외(시간)</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="E16" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="E17" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" t="inlineStr">
         <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
           <t>교대시간(분)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="20">
+      <c r="A20" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>최영필</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>급여 세부내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>근무시간(시간)</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>8</v>
-      </c>
-      <c r="I20" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>8</v>
-      </c>
-      <c r="S20" t="n">
-        <v>8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>8</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>8</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>205</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>총 근무시간</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>총 복무규정시간</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="E21" t="inlineStr">
         <is>
-          <t>복무규정시간(시간)</t>
-        </is>
-      </c>
-      <c r="AL21" t="n">
+          <t>근무시간(시간)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI21" t="n">
         <v>205</v>
       </c>
-      <c r="AM21" t="n">
-        <v>120</v>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>총 근무시간</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>총 복무규정시간</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="E22" t="inlineStr">
         <is>
-          <t>시간외(시간)</t>
-        </is>
-      </c>
-      <c r="AI22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>시간외(시간)</t>
-        </is>
+          <t>복무규정시간(시간)</t>
+        </is>
+      </c>
+      <c r="AL22" t="n">
+        <v>205</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23">
       <c r="E23" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
-        </is>
+          <t>시간외(시간)</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>130</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
+          <t>시간외(시간)</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="E24" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="E25" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="E26" t="inlineStr">
         <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AM26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
           <t>교대시간(분)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AL19:AM19"/>
+    <mergeCell ref="AL20:AM20"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="AL11:AM11"/>
+    <mergeCell ref="AL12:AM12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
